--- a/Shablon/TDS2014 old.xlsx
+++ b/Shablon/TDS2014 old.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="170">
   <si>
     <t>5 В/дел</t>
   </si>
@@ -778,13 +778,6 @@
       </rPr>
       <t>Инструкция. "Осциллографы цифровые TDS1002, TDS1012, TDS2002, TDS2012, TDS2014, TDS2022, TDS2024" Методика поверки 071-1074-00МП</t>
     </r>
-  </si>
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"
-СГМетр, лаборатория средств электрорадиотехнических измерений
-125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23
-Уникальный номер об аккредитации в реестре аккредитованных лиц № РОСС СОБ 3.00231.2014
-Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.ru</t>
   </si>
   <si>
     <r>
@@ -1367,6 +1360,48 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1376,53 +1411,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1754,46 +1747,44 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="A1" s="31"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:10" s="14" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:10" s="14" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
+      <c r="A3" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
     </row>
     <row r="4" spans="1:10" s="14" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" s="14" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1825,17 +1816,17 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="1:10" s="14" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
       <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" s="14" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1862,96 +1853,96 @@
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="14" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43" t="s">
+      <c r="F12" s="39"/>
+      <c r="G12" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="43"/>
+      <c r="H12" s="40"/>
     </row>
     <row r="13" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="45" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="30"/>
+      <c r="G13" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="28"/>
+    </row>
+    <row r="14" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="30"/>
-    </row>
-    <row r="14" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="45" t="s">
+      <c r="F14" s="30"/>
+      <c r="G14" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="28"/>
+    </row>
+    <row r="15" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="30"/>
-    </row>
-    <row r="15" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="45" t="s">
-        <v>170</v>
-      </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="30" t="s">
+      <c r="F15" s="30"/>
+      <c r="G15" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="30"/>
+      <c r="H15" s="28"/>
     </row>
     <row r="16" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30" t="s">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="30"/>
+      <c r="H16" s="28"/>
     </row>
     <row r="17" spans="1:10" s="14" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30" t="s">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="H17" s="30"/>
+      <c r="H17" s="28"/>
     </row>
     <row r="18" spans="1:10" s="14" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
@@ -1962,17 +1953,17 @@
       <c r="F18" s="20"/>
     </row>
     <row r="19" spans="1:10" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
       <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:10" s="14" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2027,14 +2018,14 @@
     </row>
     <row r="26" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:10" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
     </row>
     <row r="28" spans="1:10" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
@@ -2069,18 +2060,18 @@
         <v>0</v>
       </c>
       <c r="B30" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="D30" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="E30" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="28" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2089,162 +2080,162 @@
         <v>1</v>
       </c>
       <c r="B31" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="D31" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="E31" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="30"/>
+      <c r="F31" s="28"/>
     </row>
     <row r="32" spans="1:10" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B32" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="D32" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="E32" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="30"/>
+      <c r="F32" s="28"/>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B33" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="D33" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="E33" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F33" s="30"/>
+      <c r="F33" s="28"/>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B34" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="D34" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="E34" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="E34" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="F34" s="30"/>
+      <c r="F34" s="28"/>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B35" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="D35" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="E35" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="F35" s="30"/>
+      <c r="F35" s="28"/>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="D36" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="E36" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F36" s="30"/>
+      <c r="F36" s="28"/>
     </row>
     <row r="37" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B37" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="D37" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="E37" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="F37" s="30"/>
+      <c r="F37" s="28"/>
     </row>
     <row r="38" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="D38" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="E38" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F38" s="30"/>
+      <c r="F38" s="28"/>
     </row>
     <row r="39" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B39" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="D39" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="E39" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="E39" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F39" s="30" t="s">
+      <c r="F39" s="28" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2253,32 +2244,32 @@
         <v>10</v>
       </c>
       <c r="B40" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="D40" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="E40" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="F40" s="30"/>
+      <c r="F40" s="28"/>
     </row>
     <row r="41" spans="1:9" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="42" spans="1:9" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
     </row>
     <row r="43" spans="1:9" s="1" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="13"/>
@@ -2313,7 +2304,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4" t="s">
@@ -2328,7 +2319,7 @@
         <v>18</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
@@ -2343,7 +2334,7 @@
         <v>19</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4" t="s">
@@ -2358,7 +2349,7 @@
         <v>20</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4" t="s">
@@ -2373,7 +2364,7 @@
         <v>21</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
@@ -2412,18 +2403,18 @@
         <v>0</v>
       </c>
       <c r="B54" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="D54" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="26" t="s">
+      <c r="E54" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="E54" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F54" s="27" t="s">
+      <c r="F54" s="41" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2432,180 +2423,180 @@
         <v>1</v>
       </c>
       <c r="B55" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="D55" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="D55" s="26" t="s">
+      <c r="E55" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="E55" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="F55" s="28"/>
+      <c r="F55" s="42"/>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B56" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C56" s="26" t="s">
+      <c r="D56" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="26" t="s">
+      <c r="E56" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E56" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="F56" s="28"/>
+      <c r="F56" s="42"/>
     </row>
     <row r="57" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B57" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="D57" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="D57" s="26" t="s">
+      <c r="E57" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="E57" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="F57" s="28"/>
+      <c r="F57" s="42"/>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B58" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="26" t="s">
+      <c r="D58" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="26" t="s">
+      <c r="E58" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F58" s="28"/>
+      <c r="F58" s="42"/>
     </row>
     <row r="59" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B59" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="D59" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="26" t="s">
+      <c r="E59" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="F59" s="28"/>
+      <c r="F59" s="42"/>
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B60" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="C60" s="26" t="s">
+      <c r="D60" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="D60" s="26" t="s">
+      <c r="E60" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="E60" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="F60" s="28"/>
+      <c r="F60" s="42"/>
     </row>
     <row r="61" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B61" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C61" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="C61" s="26" t="s">
+      <c r="D61" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="E61" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="E61" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="F61" s="28"/>
+      <c r="F61" s="42"/>
     </row>
     <row r="62" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B62" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="C62" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="C62" s="26" t="s">
+      <c r="D62" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="D62" s="26" t="s">
+      <c r="E62" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="E62" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="F62" s="28"/>
+      <c r="F62" s="42"/>
     </row>
     <row r="63" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B63" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="C63" s="26" t="s">
+      <c r="D63" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="D63" s="26" t="s">
+      <c r="E63" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="E63" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="F63" s="28"/>
+      <c r="F63" s="42"/>
     </row>
     <row r="64" spans="1:6" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B64" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C64" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="C64" s="26" t="s">
+      <c r="D64" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="D64" s="26" t="s">
+      <c r="E64" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="E64" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F64" s="29"/>
+      <c r="F64" s="43"/>
     </row>
     <row r="65" spans="1:8" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="21"/>
@@ -2745,16 +2736,11 @@
     <row r="182" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F54:F64"/>
+    <mergeCell ref="F30:F38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G14:H14"/>
@@ -2768,11 +2754,16 @@
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="F54:F64"/>
-    <mergeCell ref="F30:F38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
